--- a/sample_excel/Naninovel版演出表格.xlsx
+++ b/sample_excel/Naninovel版演出表格.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\视觉小说项目\【表格演出工具】dev\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\视觉小说项目\【表格演出工具】git仓库\sample_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{158A7333-6BAE-4C82-91B8-B173C76FA88F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A697FAE5-2D31-4B26-9C18-F2749B4DD3EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sample_sheet" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
     <definedName name="TintList">OFFSET(参数表!$Q$2,0,0,COUNTA(参数表!$Q:$Q)-1,1)</definedName>
     <definedName name="TransitionList">OFFSET(参数表!$R$2,0,0,COUNTA(参数表!$R:$R)-1,1)</definedName>
     <definedName name="TransitionTypeList">OFFSET(参数表!$S$2,0,0,COUNTA(参数表!$S:$S)-1,1)</definedName>
-    <definedName name="VarientList">OFFSET(参数表!$T$2,0,0,COUNTA(参数表!$T:$T)-1,1)</definedName>
+    <definedName name="VariantList">OFFSET(参数表!$T$2,0,0,COUNTA(参数表!$T:$T)-1,1)</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -172,9 +172,6 @@
     <t>TransChar</t>
   </si>
   <si>
-    <t>Varient</t>
-  </si>
-  <si>
     <t>Pose</t>
   </si>
   <si>
@@ -437,6 +434,10 @@
   </si>
   <si>
     <t>Character</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Variant</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1091,43 +1092,43 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BI20"/>
-  <sheetFormatPr defaultRowHeight="11.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="11.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="4.58203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="40.58203125" style="1" customWidth="1"/>
+    <col min="1" max="2" width="4.5546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="40.5546875" style="1" customWidth="1"/>
     <col min="4" max="4" width="8.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="60.58203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="60.5546875" style="1" customWidth="1"/>
     <col min="6" max="8" width="8.6640625" style="5" customWidth="1"/>
-    <col min="9" max="10" width="8.58203125" style="6" customWidth="1"/>
+    <col min="9" max="10" width="8.5546875" style="6" customWidth="1"/>
     <col min="11" max="11" width="8.6640625" style="17" customWidth="1"/>
-    <col min="12" max="12" width="12.58203125" style="15" customWidth="1"/>
-    <col min="13" max="14" width="8.58203125" style="15" customWidth="1"/>
-    <col min="15" max="16" width="10.58203125" style="15" customWidth="1"/>
-    <col min="17" max="17" width="8.58203125" style="15" customWidth="1"/>
-    <col min="18" max="19" width="8.58203125" style="16" customWidth="1"/>
-    <col min="20" max="23" width="8.58203125" style="7" customWidth="1"/>
-    <col min="24" max="25" width="10.58203125" style="7" customWidth="1"/>
+    <col min="12" max="12" width="12.5546875" style="15" customWidth="1"/>
+    <col min="13" max="14" width="8.5546875" style="15" customWidth="1"/>
+    <col min="15" max="16" width="10.5546875" style="15" customWidth="1"/>
+    <col min="17" max="17" width="8.5546875" style="15" customWidth="1"/>
+    <col min="18" max="19" width="8.5546875" style="16" customWidth="1"/>
+    <col min="20" max="23" width="8.5546875" style="7" customWidth="1"/>
+    <col min="24" max="25" width="10.5546875" style="7" customWidth="1"/>
     <col min="26" max="26" width="8.6640625" style="8" customWidth="1"/>
     <col min="27" max="34" width="8.6640625" style="2" customWidth="1"/>
-    <col min="35" max="35" width="12.58203125" style="2" customWidth="1"/>
+    <col min="35" max="35" width="12.5546875" style="2" customWidth="1"/>
     <col min="36" max="36" width="8.6640625" style="2" customWidth="1"/>
-    <col min="37" max="37" width="8.58203125" style="9" customWidth="1"/>
-    <col min="38" max="38" width="16.58203125" style="10" customWidth="1"/>
-    <col min="39" max="41" width="8.58203125" style="11" customWidth="1"/>
+    <col min="37" max="37" width="8.5546875" style="9" customWidth="1"/>
+    <col min="38" max="38" width="16.5546875" style="10" customWidth="1"/>
+    <col min="39" max="41" width="8.5546875" style="11" customWidth="1"/>
     <col min="42" max="42" width="8.6640625" style="8" customWidth="1"/>
     <col min="43" max="51" width="8.6640625" style="3" customWidth="1"/>
     <col min="52" max="52" width="8.6640625" style="12" customWidth="1"/>
-    <col min="53" max="54" width="16.58203125" style="12" customWidth="1"/>
-    <col min="55" max="55" width="12.58203125" style="13" customWidth="1"/>
-    <col min="56" max="56" width="20.58203125" style="13" customWidth="1"/>
-    <col min="57" max="58" width="16.58203125" style="13" customWidth="1"/>
-    <col min="59" max="59" width="10.58203125" style="14" customWidth="1"/>
-    <col min="60" max="61" width="10.58203125" style="4" customWidth="1"/>
+    <col min="53" max="54" width="16.5546875" style="12" customWidth="1"/>
+    <col min="55" max="55" width="12.5546875" style="13" customWidth="1"/>
+    <col min="56" max="56" width="20.5546875" style="13" customWidth="1"/>
+    <col min="57" max="58" width="16.5546875" style="13" customWidth="1"/>
+    <col min="59" max="59" width="10.5546875" style="14" customWidth="1"/>
+    <col min="60" max="61" width="10.5546875" style="4" customWidth="1"/>
     <col min="62" max="89" width="8.6640625" style="1" customWidth="1"/>
     <col min="90" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1255,165 +1256,165 @@
         <v>41</v>
       </c>
       <c r="AQ1" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="AR1" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="AR1" s="3" t="s">
+      <c r="AS1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AS1" s="3" t="s">
+      <c r="AT1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="AT1" s="3" t="s">
+      <c r="AU1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="AU1" s="3" t="s">
+      <c r="AV1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="AV1" s="3" t="s">
+      <c r="AW1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AW1" s="3" t="s">
+      <c r="AX1" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AX1" s="3" t="s">
+      <c r="AY1" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="AY1" s="3" t="s">
+      <c r="AZ1" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="AZ1" s="12" t="s">
+      <c r="BA1" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="BA1" s="12" t="s">
+      <c r="BB1" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="BB1" s="12" t="s">
+      <c r="BC1" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="BC1" s="13" t="s">
+      <c r="BD1" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="BD1" s="13" t="s">
+      <c r="BE1" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="BE1" s="13" t="s">
+      <c r="BF1" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="BF1" s="13" t="s">
+      <c r="BG1" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="BG1" s="14" t="s">
+      <c r="BH1" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="BH1" s="4" t="s">
+      <c r="BI1" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="BI1" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="2" spans="1:61" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:61" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:61" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="H4" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5" spans="1:61" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>69</v>
       </c>
       <c r="J5" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I6" s="6">
         <v>0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>72</v>
-      </c>
       <c r="G7" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J7" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L8" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="L8" s="15" t="s">
+      <c r="M8" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="M8" s="15" t="s">
+      <c r="N8" s="15" t="s">
         <v>75</v>
-      </c>
-      <c r="N8" s="15" t="s">
-        <v>76</v>
       </c>
       <c r="O8" s="15">
         <v>2</v>
@@ -1425,15 +1426,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="T9" s="7" t="s">
         <v>77</v>
-      </c>
-      <c r="T9" s="7" t="s">
-        <v>78</v>
       </c>
       <c r="U9" s="7">
         <v>0.5</v>
@@ -1451,15 +1452,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:61" x14ac:dyDescent="0.25">
       <c r="Z10" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA10" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="AA10" s="2" t="s">
+      <c r="AC10" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="AC10" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="AD10" s="2">
         <v>1</v>
@@ -1471,7 +1472,7 @@
         <v>0</v>
       </c>
       <c r="AH10" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AI10" s="2">
         <v>90</v>
@@ -1480,15 +1481,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="E11" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="T11" s="7" t="s">
         <v>83</v>
-      </c>
-      <c r="T11" s="7" t="s">
-        <v>84</v>
       </c>
       <c r="U11" s="7">
         <v>0</v>
@@ -1503,27 +1504,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="E12" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA12" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="AA12" s="2" t="s">
+      <c r="AP12" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AQ12" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="AP12" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="AQ12" s="3" t="s">
+      <c r="AR12" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="AR12" s="3" t="s">
+      <c r="AS12" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="AS12" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="AU12" s="3">
         <v>1</v>
@@ -1532,7 +1533,7 @@
         <v>1</v>
       </c>
       <c r="AW12" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AX12" s="3" t="b">
         <v>1</v>
@@ -1541,69 +1542,69 @@
         <v>1</v>
       </c>
       <c r="AZ12" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="BA12" s="12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="BB12" s="12" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:61" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="AQ13" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="AQ13" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="14" spans="1:61" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="BC14" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="BC14" s="13" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="15" spans="1:61" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
       <c r="E15" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="BC15" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="BC15" s="13" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="16" spans="1:61" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
       <c r="E16" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z16" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="Z16" s="8" t="s">
+      <c r="AB16" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="AB16" s="2" t="s">
+      <c r="AE16" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="AE16" s="2" t="s">
+      <c r="BC16" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="BC16" s="13" t="s">
-        <v>102</v>
-      </c>
       <c r="BD16" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="BE16" s="13">
         <v>1</v>
@@ -1612,57 +1613,57 @@
         <v>1</v>
       </c>
       <c r="BH16" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="17" spans="1:61" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
       <c r="E17" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="Z17" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC17" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="Z17" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="AC17" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="BG17" s="14">
         <v>3</v>
       </c>
       <c r="BH17" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="18" spans="1:61" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="18" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
       <c r="E18" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="BH18" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="BH18" s="4" t="s">
+      <c r="BI18" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="BI18" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="19" spans="1:61" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>17</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K19" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="K19" s="17" t="s">
+    </row>
+    <row r="20" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="C20" s="1" t="s">
         <v>110</v>
-      </c>
-    </row>
-    <row r="20" spans="1:61" x14ac:dyDescent="0.3">
-      <c r="C20" s="1" t="s">
-        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -1742,7 +1743,7 @@
       <formula1>CharacterList</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AR2:AR1048576" xr:uid="{00000000-0002-0000-0000-000010000000}">
-      <formula1>VarientList</formula1>
+      <formula1>VariantList</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS2:AS1048576" xr:uid="{00000000-0002-0000-0000-000011000000}">
       <formula1>PoseList</formula1>
@@ -1765,27 +1766,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:U8"/>
-  <sheetFormatPr defaultColWidth="16.58203125" defaultRowHeight="11.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="16.5546875" defaultRowHeight="11.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16" width="16.58203125" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="16.58203125" style="1"/>
+    <col min="1" max="16" width="16.5546875" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="16.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>33</v>
@@ -1797,7 +1798,7 @@
         <v>27</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>40</v>
@@ -1812,197 +1813,197 @@
         <v>11</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S1" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="T1" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="U1" s="18"/>
+    </row>
+    <row r="2" spans="1:21" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="T1" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="U1" s="18"/>
-    </row>
-    <row r="2" spans="1:21" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="H2" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J2" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L2" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="O2" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="P2" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q2" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="S2" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="T2" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="U2" s="18"/>
+    </row>
+    <row r="3" spans="1:21" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="J2" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="L2" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="M2" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="O2" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="P2" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q2" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="S2" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="T2" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="U2" s="18"/>
-    </row>
-    <row r="3" spans="1:21" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="H3" s="19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J3" s="18"/>
       <c r="K3" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L3" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="N3" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="O3" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="P3" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="L3" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="N3" s="18" t="s">
+      <c r="Q3" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="O3" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="P3" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q3" s="18" t="s">
-        <v>122</v>
-      </c>
       <c r="R3" s="18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="S3" s="18" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="T3" s="18"/>
       <c r="U3" s="18"/>
     </row>
-    <row r="4" spans="1:21" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D4" s="19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J4" s="19"/>
       <c r="M4" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="N4" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="N4" s="19" t="s">
+      <c r="O4" s="18" t="s">
         <v>124</v>
-      </c>
-      <c r="O4" s="18" t="s">
-        <v>125</v>
       </c>
       <c r="P4" s="18"/>
       <c r="Q4" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="R4" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="S4" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="T4" s="18"/>
+    </row>
+    <row r="5" spans="1:21" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D5" s="19" t="s">
         <v>126</v>
-      </c>
-      <c r="R4" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="S4" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="T4" s="18"/>
-    </row>
-    <row r="5" spans="1:21" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D5" s="19" t="s">
-        <v>127</v>
       </c>
       <c r="I5" s="19"/>
       <c r="M5" s="18"/>
       <c r="N5" s="19" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O5" s="18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P5" s="18"/>
       <c r="R5" s="19" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L6" s="19"/>
     </row>
-    <row r="7" spans="1:21" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L7" s="19"/>
     </row>
-    <row r="8" spans="1:21" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L8" s="19"/>
     </row>
   </sheetData>

--- a/sample_excel/Naninovel版演出表格.xlsx
+++ b/sample_excel/Naninovel版演出表格.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\视觉小说项目\【表格演出工具】git仓库\sample_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A697FAE5-2D31-4B26-9C18-F2749B4DD3EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E21D82F5-3902-48FD-8094-20A5E557583B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="132">
   <si>
     <t>Index</t>
   </si>
@@ -438,6 +438,10 @@
   </si>
   <si>
     <t>Variant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TransitionSub</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1091,7 +1095,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BI20"/>
+  <dimension ref="A1:BJ20"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="11.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="4.5546875" style="1" customWidth="1"/>
@@ -1119,16 +1123,16 @@
     <col min="43" max="51" width="8.6640625" style="3" customWidth="1"/>
     <col min="52" max="52" width="8.6640625" style="12" customWidth="1"/>
     <col min="53" max="54" width="16.5546875" style="12" customWidth="1"/>
-    <col min="55" max="55" width="12.5546875" style="13" customWidth="1"/>
-    <col min="56" max="56" width="20.5546875" style="13" customWidth="1"/>
-    <col min="57" max="58" width="16.5546875" style="13" customWidth="1"/>
-    <col min="59" max="59" width="10.5546875" style="14" customWidth="1"/>
-    <col min="60" max="61" width="10.5546875" style="4" customWidth="1"/>
-    <col min="62" max="89" width="8.6640625" style="1" customWidth="1"/>
-    <col min="90" max="16384" width="8.6640625" style="1"/>
+    <col min="55" max="56" width="12.5546875" style="13" customWidth="1"/>
+    <col min="57" max="57" width="20.5546875" style="13" customWidth="1"/>
+    <col min="58" max="59" width="16.5546875" style="13" customWidth="1"/>
+    <col min="60" max="60" width="10.5546875" style="14" customWidth="1"/>
+    <col min="61" max="62" width="10.5546875" style="4" customWidth="1"/>
+    <col min="63" max="90" width="8.6640625" style="1" customWidth="1"/>
+    <col min="91" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1295,25 +1299,28 @@
         <v>52</v>
       </c>
       <c r="BD1" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="BE1" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="BE1" s="13" t="s">
+      <c r="BF1" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="BF1" s="13" t="s">
+      <c r="BG1" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="BG1" s="14" t="s">
+      <c r="BH1" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="BH1" s="4" t="s">
+      <c r="BI1" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="BI1" s="4" t="s">
+      <c r="BJ1" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1327,7 +1334,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1338,7 +1345,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1352,7 +1359,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1366,7 +1373,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1380,7 +1387,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1400,7 +1407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1426,7 +1433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1452,7 +1459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:62" x14ac:dyDescent="0.25">
       <c r="Z10" s="8" t="s">
         <v>78</v>
       </c>
@@ -1481,7 +1488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -1504,7 +1511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -1551,7 +1558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -1562,7 +1569,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="14" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -1573,7 +1580,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="15" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -1584,7 +1591,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="16" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -1603,20 +1610,20 @@
       <c r="BC16" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="BD16" s="13" t="s">
+      <c r="BE16" s="13" t="s">
         <v>81</v>
-      </c>
-      <c r="BE16" s="13">
-        <v>1</v>
       </c>
       <c r="BF16" s="13">
         <v>1</v>
       </c>
-      <c r="BH16" s="4" t="s">
+      <c r="BG16" s="13">
+        <v>1</v>
+      </c>
+      <c r="BI16" s="4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="17" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -1629,28 +1636,28 @@
       <c r="AC17" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="BG17" s="14">
+      <c r="BH17" s="14">
         <v>3</v>
       </c>
-      <c r="BH17" s="4" t="s">
+      <c r="BI17" s="4" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="18" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="BH18" s="4" t="s">
+      <c r="BI18" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="BI18" s="4" t="s">
+      <c r="BJ18" s="4" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="19" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -1661,7 +1668,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="20" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:62" x14ac:dyDescent="0.25">
       <c r="C20" s="1" t="s">
         <v>110</v>
       </c>
@@ -1712,10 +1719,10 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA2:BA1048576" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>AnimationList</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BD2:BD1048576 AH2:AH1048576" xr:uid="{00000000-0002-0000-0000-000006000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BE2:BE1048576 AH2:AH1048576" xr:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>DissolveList</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC2:BC1048576" xr:uid="{00000000-0002-0000-0000-000007000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC2:BD1048576" xr:uid="{00000000-0002-0000-0000-000007000000}">
       <formula1>TransitionList</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F1048576" xr:uid="{00000000-0002-0000-0000-000008000000}">
@@ -1751,7 +1758,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2:AW1048576" xr:uid="{00000000-0002-0000-0000-000012000000}">
       <formula1>TintList</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH2:BH1048576" xr:uid="{00000000-0002-0000-0000-000013000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BI2:BI1048576" xr:uid="{00000000-0002-0000-0000-000013000000}">
       <formula1>PrinterList</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB1048576" xr:uid="{00000000-0002-0000-0000-000014000000}">
